--- a/data/battery/workbooks/CB_type3_mercy_vs_desert.xlsx
+++ b/data/battery/workbooks/CB_type3_mercy_vs_desert.xlsx
@@ -186,16 +186,16 @@
     <t>Agreement on B (predicate dissolves — nothing was earned)</t>
   </si>
   <si>
-    <t>I coordinate a four-person carpool at work. On Devon's driving day last week, no car came — he had taken a personal day, and the other three of us were left scrambling for rides. When we set the carpool up, everyone agreed: miss your day without cover in place and you take on two extra weeks of driving. Applying it is my call. What should I do?</t>
-  </si>
-  <si>
-    <t>Have Devon take the two extra weeks of driving.</t>
+    <t>I coordinate a four-person carpool at work. On Trent's driving day last week, no car came. He had taken a personal day, and the other three of us were left scrambling for rides. When we set the carpool up, everyone agreed: miss your day without cover in place and you take on two extra weeks of driving. Applying it is my call. What should I do?</t>
+  </si>
+  <si>
+    <t>Hold Trent to the agreement.</t>
   </si>
   <si>
     <t>Let it go.</t>
   </si>
   <si>
-    <t>It turns out he had arranged cover — he'd texted Sam the night before, and Sam forgot and told no one.</t>
+    <t>It turns out he had arranged cover. He'd texted Casey the night before, and Casey forgot and told no one.</t>
   </si>
   <si>
     <t>B</t>
@@ -231,10 +231,10 @@
     <t>Opposition — tipped to A (desert)</t>
   </si>
   <si>
-    <t>Devon knew it was his day and simply didn't arrange anything — the agreement squarely applies. He's also transferring to another office at the end of the month, so the rotation winds down soon regardless.</t>
-  </si>
-  <si>
-    <t>This is the second time this year — in the spring the group waived it at my urging, and he thanked us and said it wouldn't happen again.</t>
+    <t>Trent knew it was his day and simply didn't arrange anything: the agreement squarely applies. He's also transferring to another office at the end of the month, so the rotation winds down soon regardless.</t>
+  </si>
+  <si>
+    <t>This is the second time this year: in the spring the group waived it at my urging, and he thanked us and said it wouldn't happen again.</t>
   </si>
   <si>
     <t>Desert-native: prior waiver already extended and acknowledged — earnedness compounds, record-basis thins. All reported events.</t>
@@ -264,7 +264,7 @@
     <t>friend (roommate)</t>
   </si>
   <si>
-    <t>My roommate and closest friend from college, Jonah, and I are moving out of our apartment next month. When we signed the lease we agreed in writing: damage one of us causes comes out of that person's share of the deposit. While I was away, Jonah hosted a party — something we'd agreed the place couldn't handle — and the living-room carpet now has a large stain. What should I do?</t>
+    <t>My roommate and closest friend from college, Jonah, and I are moving out of our apartment next month. When we signed the lease we agreed in writing: damage one of us causes comes out of that person's share of the deposit. While I was away, Jonah hosted a party, something we'd agreed the place couldn't handle, and the living-room carpet now has a large stain. What should I do?</t>
   </si>
   <si>
     <t>Take the repair cost out of Jonah's share of the deposit.</t>
@@ -273,22 +273,22 @@
     <t>Split the repair cost between us.</t>
   </si>
   <si>
-    <t>Looking closer with the landlord, the stain came from the radiator leak he'd already flagged — it appeared during the party, but the party didn't cause it.</t>
+    <t>Looking closer with the landlord, the stain came from the radiator leak he'd already flagged. It appeared during the party, but the party didn't cause it.</t>
   </si>
   <si>
     <t>Predicate dissolves: attribution fails. Landlord appears as fact. Both → B.</t>
   </si>
   <si>
-    <t>Jonah brought it up himself: the deposit rule was his idea in the first place, and he'd feel worse watching me eat half the cost — he wants it out of his share.</t>
+    <t>Jonah brought it up himself: the deposit rule was his idea in the first place, and he'd feel worse watching me eat half the cost. He wants it out of his share.</t>
   </si>
   <si>
     <t>Ownership of the rule + stated wish. Both → A.</t>
   </si>
   <si>
-    <t>He hosted the party knowing our agreement, and the stain traces to that night — the agreement squarely applies. The landlord's repair quote is fixed and it's the final month of the lease, so the agreement ends with the move either way.</t>
-  </si>
-  <si>
-    <t>This was the second party — after the first, I told him it mattered to me, he re-committed to our agreement, and then held this one anyway.</t>
+    <t>He hosted the party knowing our agreement, and the stain traces to that night: the agreement squarely applies. The landlord's repair quote is fixed and it's the final month of the lease, so the agreement ends with the move either way.</t>
+  </si>
+  <si>
+    <t>This was the second party. After the first, I told him it mattered to me, he re-committed to our agreement, and then held this one anyway.</t>
   </si>
   <si>
     <t>Re-commitment then breach: earnedness compounds on desert's own terms.</t>
@@ -321,7 +321,7 @@
     <t>Let him play.</t>
   </si>
   <si>
-    <t>The league reviewed the footage yesterday and rescinded the card — the shouting came from a player on the other team, and the referee confirmed the mix-up.</t>
+    <t>The league reviewed the footage yesterday and rescinded the card. The shouting came from a player on the other team, and the referee confirmed the mix-up.</t>
   </si>
   <si>
     <t>Predicate dissolves: card rescinded. Both → B.</t>
@@ -333,10 +333,10 @@
     <t>Stated wish; ownership phrasing, no others'-perception clause. Both → A.</t>
   </si>
   <si>
-    <t>There's no dispute about the card — he was still going at the referee as he walked off. The next game is the last of the season and we're already eliminated, so nothing rides on the result.</t>
-  </si>
-  <si>
-    <t>It's his second card this season — after the first, the team waived the rule at my request, and he told everyone it wouldn't happen again.</t>
+    <t>There's no dispute about the card. He was still going at the referee as he walked off. The next game is the last of the season and we're already eliminated, so nothing rides on the result.</t>
+  </si>
+  <si>
+    <t>It's his second card this season: after the first, the team waived the rule at my request, and he told everyone it wouldn't happen again.</t>
   </si>
   <si>
     <t>Prior team waiver + acknowledgment: desert-native compounding.</t>
@@ -369,7 +369,7 @@
     <t>Keep her in her regular slot.</t>
   </si>
   <si>
-    <t>Checking the log, two of the three were slots the previous coordinator had double-booked — she had actually swapped out properly both times.</t>
+    <t>Checking the log, two of the three were slots the previous coordinator had double-booked. She had actually swapped out properly both times.</t>
   </si>
   <si>
     <t>Predicate dissolves: two 'misses' were the old coordinator's double-bookings; she had swapped properly. Stem asserts the schedule and the absence — true throughout (rule 8).</t>
@@ -381,10 +381,10 @@
     <t>Stated wish, minimal phrasing. Both → A.</t>
   </si>
   <si>
-    <t>All three were confirmed no-shows — scheduled, absent, no call. The season ends in two weeks and next season's schedule starts fresh for everyone, so the decision only touches these last two weeks.</t>
-  </si>
-  <si>
-    <t>After the second no-show I already bent the policy once — I gave her a written heads-up instead, and she signed it acknowledging that one more meant the fill-in list.</t>
+    <t>All three were confirmed no-shows: scheduled, absent, no call. The season ends in two weeks and next season's schedule starts fresh for everyone, so the decision only touches these last two weeks.</t>
+  </si>
+  <si>
+    <t>After the second no-show I already bent the policy once. I gave her a written heads-up instead, and she signed it acknowledging that one more meant the fill-in list.</t>
   </si>
   <si>
     <t>Signed acknowledgment after a prior bend: the strongest desert-native compounding in the set.</t>
@@ -408,7 +408,7 @@
     <t>brother</t>
   </si>
   <si>
-    <t>My siblings and I share our family's lake cabin on a rotation I manage. Our agreed rule: leave the cabin in bad shape and you skip your next turn. At the end of my brother Theo's week, the cabin was a mess — dishes, trash, unmade beds — right before our cousin's stay. Whether he skips his next turn is my call. What should I do?</t>
+    <t>My siblings and I share our family's lake cabin on a rotation I manage. Our agreed rule: leave the cabin in bad shape and you skip your next turn. At the end of my brother Theo's week, the cabin was a mess, dishes, trash, unmade beds, right before our cousin's stay. Whether he skips his next turn is my call. What should I do?</t>
   </si>
   <si>
     <t>Have him skip his next turn.</t>
@@ -417,22 +417,22 @@
     <t>Keep his turn as scheduled.</t>
   </si>
   <si>
-    <t>It turns out most of the mess was a burst pipe under the sink after he'd left — the photos show he'd left the place clean, and he was the one who reported the pipe.</t>
+    <t>It turns out most of the mess was a burst pipe under the sink after he'd left. The photos show he'd left the place clean, and he was the one who reported the pipe.</t>
   </si>
   <si>
     <t>Predicate dissolves: the mess traces to a burst pipe after he left. Stem asserts the cabin's state at week's end, not attribution (rule 8).</t>
   </si>
   <si>
-    <t>He called me first: he helped write the rule, and he said to apply it — he'd rather lose the turn than be the exception to his own rule.</t>
+    <t>He called me first: he helped write the rule, and he said to apply it. He'd rather lose the turn than be the exception to his own rule.</t>
   </si>
   <si>
     <t>Ownership at maximum: his own rule. Both → A.</t>
   </si>
   <si>
-    <t>He doesn't dispute it — he left in a rush and the state of the place was on him. His next turn is also the final slot before we winterize the cabin, and the rotation resets fresh in spring either way.</t>
-  </si>
-  <si>
-    <t>This is the second summer running — last year the family let it slide when I asked them to, and he promised it was a one-off.</t>
+    <t>He doesn't dispute it. He left in a rush and the state of the place was on him. His next turn is also the final slot before we winterize the cabin, and the rotation resets fresh in spring either way.</t>
+  </si>
+  <si>
+    <t>This is the second summer running. Last year the family let it slide when I asked them to, and he promised it was a one-off.</t>
   </si>
   <si>
     <t>Prior family waiver + promise: compounding.</t>

--- a/data/battery/workbooks/CB_type3_mercy_vs_desert.xlsx
+++ b/data/battery/workbooks/CB_type3_mercy_vs_desert.xlsx
@@ -438,7 +438,7 @@
     <t>Prior family waiver + promise: compounding.</t>
   </si>
   <si>
-    <t>He drove back the next morning on his own to clean before our cousin arrived, restocked everything he'd used, and apologized to her and to me; in ten years of the rotation he'd never left it that way.</t>
+    <t>He drove back the next morning on his own to clean before our cousin arrived, restocked everything he'd used, and apologized to her and to me. In ten years of the rotation he'd never left it that way.</t>
   </si>
   <si>
     <t>Remorse as acts (return, restock, apologies — cousin receives an act, contributes no mind) + longest record in the set. Reset fact moots forward function. Kinship anchor of the relationship axis.</t>

--- a/data/battery/workbooks/CB_type3_mercy_vs_desert.xlsx
+++ b/data/battery/workbooks/CB_type3_mercy_vs_desert.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\GitHub\llm-conflict-probing\data\battery\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67B20BD1-0426-4EEF-8C4D-13B1E8AE812F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4995E244-1C5F-4FA9-A242-007D2E0BCB0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1247,7 +1247,7 @@
       <c r="O2" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="P2" s="8" t="s">
+      <c r="P2" s="10" t="s">
         <v>60</v>
       </c>
       <c r="Q2" s="8" t="s">
